--- a/testcase google login.xlsx
+++ b/testcase google login.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="98">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -400,9 +400,6 @@
     <t>Google Sign-in page is displyed.</t>
   </si>
   <si>
-    <t>Chrome browser opnes successfully.</t>
-  </si>
-  <si>
     <t>Click the sign-in button.</t>
   </si>
   <si>
@@ -431,6 +428,12 @@
       </rPr>
       <t>and press Enter.</t>
     </r>
+  </si>
+  <si>
+    <t>Gauri Mahalle</t>
+  </si>
+  <si>
+    <t>Chrome browser opned successfully.</t>
   </si>
 </sst>
 </file>
@@ -1030,6 +1033,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1112,7 +1116,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1277,6 +1280,44 @@
         <a:xfrm>
           <a:off x="2281394" y="7366512"/>
           <a:ext cx="1951087" cy="1083085"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>99858</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>299577</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>883366</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1474838</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2319798" y="2734597"/>
+          <a:ext cx="1812822" cy="1175261"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1498,10 +1539,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
+      <c r="B1" s="50"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1509,13 +1550,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="52"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1533,10 +1574,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="39"/>
+      <c r="B2" s="40"/>
       <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1544,14 +1585,14 @@
         <v>6</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="56" t="s">
+      <c r="G2" s="40"/>
+      <c r="H2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="39"/>
+      <c r="I2" s="40"/>
       <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1572,10 +1613,10 @@
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="25.5" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="39"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1583,14 +1624,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="57">
+      <c r="F3" s="58">
         <v>46220</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="56" t="s">
+      <c r="G3" s="40"/>
+      <c r="H3" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="39"/>
+      <c r="I3" s="40"/>
       <c r="J3" s="10" t="s">
         <v>14</v>
       </c>
@@ -1641,21 +1682,21 @@
       <c r="A5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="56" t="s">
+      <c r="G5" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="40"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="41"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1676,21 +1717,21 @@
       <c r="A6" s="17">
         <v>1</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="5"/>
       <c r="F6" s="18">
         <v>1</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="40"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1711,21 +1752,21 @@
       <c r="A7" s="17">
         <v>2</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40"/>
       <c r="E7" s="5"/>
       <c r="F7" s="18">
         <v>2</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="40"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="41"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1746,17 +1787,17 @@
       <c r="A8" s="17">
         <v>3</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="40"/>
       <c r="E8" s="5"/>
       <c r="F8" s="18">
         <v>3</v>
       </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="40"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="41"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1777,17 +1818,17 @@
       <c r="A9" s="19">
         <v>4</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="43"/>
       <c r="E9" s="20"/>
       <c r="F9" s="21">
         <v>4</v>
       </c>
-      <c r="G9" s="41"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="44"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="45"/>
       <c r="K9" s="22"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1835,17 +1876,17 @@
       <c r="A11" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1864,17 +1905,17 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1">
       <c r="A12" s="4"/>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1922,23 +1963,23 @@
       <c r="A14" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="48" t="s">
+      <c r="C14" s="50"/>
+      <c r="D14" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="48" t="s">
+      <c r="E14" s="50"/>
+      <c r="F14" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="50"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="48" t="s">
+      <c r="G14" s="51"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="51"/>
+      <c r="J14" s="52"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1959,23 +2000,23 @@
       <c r="A15" s="17">
         <v>1</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="37" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="37" t="s">
+      <c r="E15" s="40"/>
+      <c r="F15" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="37" t="s">
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="40"/>
+      <c r="J15" s="41"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1996,23 +2037,23 @@
       <c r="A16" s="17">
         <v>2</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="37" t="s">
+      <c r="C16" s="40"/>
+      <c r="D16" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="39"/>
-      <c r="F16" s="37" t="s">
+      <c r="E16" s="40"/>
+      <c r="F16" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="37" t="s">
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="40"/>
+      <c r="J16" s="41"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -2033,23 +2074,23 @@
       <c r="A17" s="17">
         <v>3</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="37" t="s">
+      <c r="C17" s="40"/>
+      <c r="D17" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="39"/>
-      <c r="F17" s="37" t="s">
+      <c r="E17" s="40"/>
+      <c r="F17" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="37" t="s">
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="40"/>
+      <c r="J17" s="41"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -2070,23 +2111,23 @@
       <c r="A18" s="17">
         <v>4</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="37" t="s">
+      <c r="C18" s="40"/>
+      <c r="D18" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="37" t="s">
+      <c r="E18" s="40"/>
+      <c r="F18" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="37" t="s">
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="40"/>
+      <c r="J18" s="41"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -2107,23 +2148,23 @@
       <c r="A19" s="28">
         <v>5</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="37" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="37" t="s">
+      <c r="E19" s="40"/>
+      <c r="F19" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="37" t="s">
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="40"/>
+      <c r="J19" s="41"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2144,23 +2185,23 @@
       <c r="A20" s="28">
         <v>6</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="37" t="s">
+      <c r="C20" s="40"/>
+      <c r="D20" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="37" t="s">
+      <c r="E20" s="40"/>
+      <c r="F20" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="37" t="s">
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="40"/>
+      <c r="J20" s="41"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2181,23 +2222,23 @@
       <c r="A21" s="28">
         <v>7</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="37" t="s">
+      <c r="C21" s="40"/>
+      <c r="D21" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="37" t="s">
+      <c r="E21" s="40"/>
+      <c r="F21" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="37" t="s">
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="40"/>
+      <c r="J21" s="41"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2218,23 +2259,23 @@
       <c r="A22" s="28">
         <v>8</v>
       </c>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="37" t="s">
+      <c r="C22" s="40"/>
+      <c r="D22" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="37" t="s">
+      <c r="E22" s="40"/>
+      <c r="F22" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="37" t="s">
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="40"/>
+      <c r="J22" s="41"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2255,15 +2296,15 @@
       <c r="A23" s="28">
         <v>9</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="40"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="41"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2284,15 +2325,15 @@
       <c r="A24" s="28">
         <v>10</v>
       </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="40"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="41"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2313,15 +2354,15 @@
       <c r="A25" s="28">
         <v>11</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="40"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="41"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2342,15 +2383,15 @@
       <c r="A26" s="28">
         <v>12</v>
       </c>
-      <c r="B26" s="37"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="40"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="41"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2371,15 +2412,15 @@
       <c r="A27" s="28">
         <v>13</v>
       </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="40"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="41"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2400,15 +2441,15 @@
       <c r="A28" s="28">
         <v>14</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="40"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="41"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2429,15 +2470,15 @@
       <c r="A29" s="28">
         <v>15</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="40"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="41"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -2458,15 +2499,15 @@
       <c r="A30" s="28">
         <v>16</v>
       </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="40"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="41"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2487,15 +2528,15 @@
       <c r="A31" s="28">
         <v>17</v>
       </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="40"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="41"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2516,15 +2557,15 @@
       <c r="A32" s="28">
         <v>18</v>
       </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="40"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="41"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2545,15 +2586,15 @@
       <c r="A33" s="28">
         <v>19</v>
       </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="40"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="41"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2574,15 +2615,15 @@
       <c r="A34" s="29">
         <v>20</v>
       </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="44"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="45"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -28649,10 +28690,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
+      <c r="B1" s="50"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -28660,19 +28701,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="52"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="39"/>
+      <c r="B2" s="40"/>
       <c r="C2" s="30" t="s">
         <v>49</v>
       </c>
@@ -28680,23 +28721,23 @@
         <v>6</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="67" t="s">
-        <v>48</v>
+      <c r="F2" s="38" t="s">
+        <v>96</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="56" t="s">
+      <c r="G2" s="40"/>
+      <c r="H2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="39"/>
+      <c r="I2" s="40"/>
       <c r="J2" s="31" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="39"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="30" t="s">
         <v>48</v>
       </c>
@@ -28704,14 +28745,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="68" t="s">
+      <c r="F3" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="56" t="s">
+      <c r="G3" s="40"/>
+      <c r="H3" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="39"/>
+      <c r="I3" s="40"/>
       <c r="J3" s="32" t="s">
         <v>48</v>
       </c>
@@ -28732,93 +28773,93 @@
       <c r="A5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="56" t="s">
+      <c r="G5" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="40"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="28">
         <v>1</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="5"/>
       <c r="F6" s="18">
         <v>1</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="40"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="28">
         <v>2</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40"/>
       <c r="E7" s="5"/>
       <c r="F7" s="18">
         <v>2</v>
       </c>
-      <c r="G7" s="67" t="s">
+      <c r="G7" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="40"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="41"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="28">
         <v>3</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="40"/>
       <c r="E8" s="5"/>
       <c r="F8" s="18">
         <v>3</v>
       </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="40"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" thickBot="1">
       <c r="A9" s="29">
         <v>4</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="43"/>
       <c r="E9" s="20"/>
       <c r="F9" s="21">
         <v>4</v>
       </c>
-      <c r="G9" s="41"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="44"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="45"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="25"/>
@@ -28836,31 +28877,31 @@
       <c r="A11" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="26"/>
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" thickBot="1">
       <c r="A13" s="26"/>
@@ -28878,427 +28919,427 @@
       <c r="A14" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="48" t="s">
+      <c r="C14" s="50"/>
+      <c r="D14" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="48" t="s">
+      <c r="E14" s="50"/>
+      <c r="F14" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="50"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="48" t="s">
+      <c r="G14" s="51"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="51"/>
-    </row>
-    <row r="15" spans="1:10" ht="44.25" customHeight="1">
+      <c r="J14" s="52"/>
+    </row>
+    <row r="15" spans="1:10" ht="126" customHeight="1">
       <c r="A15" s="28">
         <v>1</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="37" t="s">
-        <v>93</v>
+      <c r="C15" s="40"/>
+      <c r="D15" s="38" t="s">
+        <v>97</v>
       </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="41"/>
     </row>
     <row r="16" spans="1:10" ht="114.75" customHeight="1">
       <c r="A16" s="28">
         <v>2</v>
       </c>
-      <c r="B16" s="37" t="s">
-        <v>96</v>
+      <c r="B16" s="38" t="s">
+        <v>95</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="37" t="s">
+      <c r="C16" s="40"/>
+      <c r="D16" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="39"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="41"/>
     </row>
     <row r="17" spans="1:10" ht="134.25" customHeight="1">
       <c r="A17" s="28">
         <v>3</v>
       </c>
-      <c r="B17" s="37" t="s">
-        <v>94</v>
+      <c r="B17" s="38" t="s">
+        <v>93</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="37" t="s">
+      <c r="C17" s="40"/>
+      <c r="D17" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="39"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="41"/>
     </row>
     <row r="18" spans="1:10" ht="108" customHeight="1">
       <c r="A18" s="28">
         <v>4</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="37" t="s">
+      <c r="C18" s="40"/>
+      <c r="D18" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="41"/>
     </row>
     <row r="19" spans="1:10" ht="30.75" customHeight="1">
       <c r="A19" s="28">
         <v>5</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="37" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="41"/>
     </row>
     <row r="20" spans="1:10" ht="39.75" customHeight="1">
       <c r="A20" s="28">
         <v>6</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="37" t="s">
+      <c r="C20" s="40"/>
+      <c r="D20" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="41"/>
     </row>
     <row r="21" spans="1:10" ht="43.5" customHeight="1">
       <c r="A21" s="28">
         <v>7</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="37" t="s">
+      <c r="C21" s="40"/>
+      <c r="D21" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="41"/>
     </row>
     <row r="22" spans="1:10" ht="27" customHeight="1">
       <c r="A22" s="28">
         <v>8</v>
       </c>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="37" t="s">
+      <c r="C22" s="40"/>
+      <c r="D22" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="41"/>
     </row>
     <row r="23" spans="1:10" hidden="1">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="40"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="41"/>
     </row>
     <row r="24" spans="1:10" ht="44.25" customHeight="1">
       <c r="A24" s="28">
         <v>9</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="37" t="s">
+      <c r="C24" s="40"/>
+      <c r="D24" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="39"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="41"/>
     </row>
     <row r="25" spans="1:10" ht="39" customHeight="1">
       <c r="A25" s="28">
         <v>10</v>
       </c>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="37" t="s">
+      <c r="C25" s="40"/>
+      <c r="D25" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="41"/>
     </row>
     <row r="26" spans="1:10" ht="100.5" customHeight="1">
       <c r="A26" s="28">
         <v>11</v>
       </c>
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="37" t="s">
+      <c r="C26" s="40"/>
+      <c r="D26" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="39"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="41"/>
     </row>
     <row r="27" spans="1:10" ht="29.25" customHeight="1">
       <c r="A27" s="28">
         <v>12</v>
       </c>
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="37" t="s">
+      <c r="C27" s="40"/>
+      <c r="D27" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="39"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="41"/>
     </row>
     <row r="28" spans="1:10" ht="28.5" customHeight="1">
       <c r="A28" s="28">
         <v>13</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="37" t="s">
+      <c r="C28" s="40"/>
+      <c r="D28" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E28" s="39"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="41"/>
     </row>
     <row r="29" spans="1:10" ht="28.5" customHeight="1">
       <c r="A29" s="28">
         <v>14</v>
       </c>
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="37" t="s">
+      <c r="C29" s="40"/>
+      <c r="D29" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="40"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="41"/>
     </row>
     <row r="30" spans="1:10" ht="32.25" customHeight="1">
       <c r="A30" s="28">
         <v>15</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="37" t="s">
+      <c r="C30" s="40"/>
+      <c r="D30" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="40"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="41"/>
     </row>
     <row r="31" spans="1:10" ht="27" customHeight="1">
       <c r="A31" s="28">
         <v>16</v>
       </c>
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="37" t="s">
+      <c r="C31" s="40"/>
+      <c r="D31" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="40"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="27" customHeight="1">
       <c r="A32" s="28">
         <v>17</v>
       </c>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="37" t="s">
+      <c r="C32" s="40"/>
+      <c r="D32" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="40"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="41"/>
     </row>
     <row r="33" spans="1:11" ht="27" customHeight="1">
       <c r="A33" s="28">
         <v>18</v>
       </c>
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="37" t="s">
+      <c r="C33" s="40"/>
+      <c r="D33" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="62"/>
-      <c r="J33" s="40"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="41"/>
     </row>
     <row r="34" spans="1:11" ht="27" customHeight="1" thickBot="1">
       <c r="A34" s="28">
         <v>19</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="41" t="s">
-        <v>95</v>
+      <c r="C34" s="43"/>
+      <c r="D34" s="42" t="s">
+        <v>94</v>
       </c>
-      <c r="E34" s="43"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="45"/>
     </row>
     <row r="35" spans="1:11" ht="52.5" customHeight="1" thickBot="1">
       <c r="A35" s="28">
         <v>20</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="41" t="s">
+      <c r="C35" s="43"/>
+      <c r="D35" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="E35" s="42"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="74"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="44"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="45"/>
     </row>
     <row r="36" spans="1:11" s="33" customFormat="1" ht="47.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A36" s="35">
         <v>21</v>
       </c>
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="65"/>
-      <c r="D36" s="63" t="s">
+      <c r="C36" s="66"/>
+      <c r="D36" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="65"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="37"/>
     </row>
     <row r="37" spans="1:11" s="33" customFormat="1" ht="27" customHeight="1">
       <c r="A37" s="34"/>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="72"/>
+      <c r="J37" s="71"/>
       <c r="K37" s="34"/>
     </row>
     <row r="38" spans="1:11">

--- a/testcase google login.xlsx
+++ b/testcase google login.xlsx
@@ -349,9 +349,6 @@
     <t>Click the Forgot email?link.</t>
   </si>
   <si>
-    <t>Click the Forgot password?link.</t>
-  </si>
-  <si>
     <t>Password recovery page opens.</t>
   </si>
   <si>
@@ -434,6 +431,9 @@
   </si>
   <si>
     <t>Chrome browser opned successfully.</t>
+  </si>
+  <si>
+    <t>Click the Forgot password? link.</t>
   </si>
 </sst>
 </file>
@@ -1169,6 +1169,11 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1207,6 +1212,11 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1245,6 +1255,11 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1284,6 +1299,11 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1322,6 +1342,11 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -28722,7 +28747,7 @@
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G2" s="40"/>
       <c r="H2" s="57" t="s">
@@ -28946,7 +28971,7 @@
       </c>
       <c r="C15" s="40"/>
       <c r="D15" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="38"/>
@@ -28960,7 +28985,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" s="40"/>
       <c r="D16" s="38" t="s">
@@ -28978,7 +29003,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" s="40"/>
       <c r="D17" s="38" t="s">
@@ -29154,11 +29179,11 @@
         <v>12</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" s="40"/>
       <c r="F27" s="38"/>
@@ -29172,11 +29197,11 @@
         <v>13</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E28" s="40"/>
       <c r="F28" s="64"/>
@@ -29190,11 +29215,11 @@
         <v>14</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" s="40"/>
       <c r="D29" s="38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E29" s="39"/>
       <c r="F29" s="60"/>
@@ -29208,11 +29233,11 @@
         <v>15</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" s="40"/>
       <c r="D30" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" s="39"/>
       <c r="F30" s="60"/>
@@ -29226,11 +29251,11 @@
         <v>16</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" s="40"/>
       <c r="D31" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="39"/>
       <c r="F31" s="60"/>
@@ -29244,11 +29269,11 @@
         <v>17</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C32" s="40"/>
       <c r="D32" s="38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E32" s="39"/>
       <c r="F32" s="60"/>
@@ -29262,11 +29287,11 @@
         <v>18</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C33" s="40"/>
       <c r="D33" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E33" s="39"/>
       <c r="F33" s="60"/>
@@ -29280,11 +29305,11 @@
         <v>19</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" s="43"/>
       <c r="D34" s="42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E34" s="44"/>
       <c r="F34" s="60"/>
@@ -29298,11 +29323,11 @@
         <v>20</v>
       </c>
       <c r="B35" s="42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" s="43"/>
       <c r="D35" s="42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E35" s="43"/>
       <c r="F35" s="73"/>

--- a/testcase google login.xlsx
+++ b/testcase google login.xlsx
@@ -346,12 +346,6 @@
     <t>Account recovery page opens.</t>
   </si>
   <si>
-    <t>Click the Forgot email?link.</t>
-  </si>
-  <si>
-    <t>Password recovery page opens.</t>
-  </si>
-  <si>
     <t>Enter password in the password field.</t>
   </si>
   <si>
@@ -403,18 +397,24 @@
     <t>User is logged out sucessfully.</t>
   </si>
   <si>
+    <t>Gauri Mahalle</t>
+  </si>
+  <si>
+    <t>Chrome browser opened successfully.</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Enter </t>
+      <t xml:space="preserve">Click the </t>
     </r>
     <r>
       <rPr>
-        <u/>
+        <b/>
         <sz val="10"/>
-        <color rgb="FF0070C0"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">http//accounts.google.com/signin </t>
+      <t>Forgot email?</t>
     </r>
     <r>
       <rPr>
@@ -423,17 +423,46 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>and press Enter.</t>
+      <t xml:space="preserve"> link.</t>
     </r>
   </si>
   <si>
-    <t>Gauri Mahalle</t>
+    <r>
+      <t xml:space="preserve">(i) Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://accounts.google.com/signin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in address bar.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(ii) press Enter.</t>
+    </r>
   </si>
   <si>
-    <t>Chrome browser opned successfully.</t>
+    <t>Enter a valid email.</t>
   </si>
   <si>
-    <t>Click the Forgot password? link.</t>
+    <t>Password page opens.</t>
   </si>
 </sst>
 </file>
@@ -443,7 +472,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -490,18 +519,22 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1033,7 +1066,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1138,15 +1171,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>96538</xdr:colOff>
+      <xdr:colOff>111901</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>205946</xdr:rowOff>
+      <xdr:rowOff>190583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>901015</xdr:colOff>
+      <xdr:colOff>916378</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>1242111</xdr:rowOff>
+      <xdr:rowOff>1226748</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1163,8 +1196,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2316893" y="12253784"/>
-          <a:ext cx="1834206" cy="1036165"/>
+          <a:off x="2331841" y="11612902"/>
+          <a:ext cx="1833791" cy="1036165"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -28707,11 +28740,12 @@
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="5" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
     <col min="6" max="6" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -28747,7 +28781,7 @@
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G2" s="40"/>
       <c r="H2" s="57" t="s">
@@ -28971,7 +29005,7 @@
       </c>
       <c r="C15" s="40"/>
       <c r="D15" s="38" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="38"/>
@@ -28985,7 +29019,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C16" s="40"/>
       <c r="D16" s="38" t="s">
@@ -29003,7 +29037,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C17" s="40"/>
       <c r="D17" s="38" t="s">
@@ -29161,7 +29195,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C26" s="40"/>
       <c r="D26" s="38" t="s">
@@ -29179,11 +29213,11 @@
         <v>12</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="38" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="E27" s="40"/>
       <c r="F27" s="38"/>
@@ -29197,11 +29231,11 @@
         <v>13</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E28" s="40"/>
       <c r="F28" s="64"/>
@@ -29215,11 +29249,11 @@
         <v>14</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C29" s="40"/>
       <c r="D29" s="38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E29" s="39"/>
       <c r="F29" s="60"/>
@@ -29233,11 +29267,11 @@
         <v>15</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C30" s="40"/>
       <c r="D30" s="38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E30" s="39"/>
       <c r="F30" s="60"/>
@@ -29251,11 +29285,11 @@
         <v>16</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C31" s="40"/>
       <c r="D31" s="38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E31" s="39"/>
       <c r="F31" s="60"/>
@@ -29269,11 +29303,11 @@
         <v>17</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C32" s="40"/>
       <c r="D32" s="38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E32" s="39"/>
       <c r="F32" s="60"/>
@@ -29287,11 +29321,11 @@
         <v>18</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C33" s="40"/>
       <c r="D33" s="38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E33" s="39"/>
       <c r="F33" s="60"/>
@@ -29305,11 +29339,11 @@
         <v>19</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C34" s="43"/>
       <c r="D34" s="42" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E34" s="44"/>
       <c r="F34" s="60"/>
@@ -29323,11 +29357,11 @@
         <v>20</v>
       </c>
       <c r="B35" s="42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C35" s="43"/>
       <c r="D35" s="42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E35" s="43"/>
       <c r="F35" s="73"/>
